--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02A79C7-23D4-49E8-AF5C-EA118D7094D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F6431B-8687-4A20-A7DC-3A11C2AF4E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="489">
   <si>
     <t>TAG</t>
   </si>
@@ -1501,6 +1501,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6023.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/V12 - _KIT_FLANGE_CAR200M L_FF350.pdf</t>
   </si>
 </sst>
 </file>
@@ -1588,9 +1591,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1603,51 +1603,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1783,29 +1746,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
+  <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="WCG20 - V/F12"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Correia Transportadora - CT- 01"/>
+        <filter val="Correia Transportadora - CT- 02"/>
+        <filter val="Correia Transportadora - CT- 03"/>
+        <filter val="Correia Transportadora - CT- 04"/>
+        <filter val="Correia Transportadora - CT-08"/>
+        <filter val="Correia Transportadora - CT-09"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2043,7 +2022,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57">
+    <row r="2" spans="1:18" ht="57" hidden="1">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -2097,7 +2076,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57">
+    <row r="3" spans="1:18" ht="57" hidden="1">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -2151,7 +2130,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57">
+    <row r="4" spans="1:18" ht="57" hidden="1">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -2205,7 +2184,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57">
+    <row r="5" spans="1:18" ht="57" hidden="1">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2298,7 +2277,7 @@
         <v>86</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>37</v>
@@ -2352,7 +2331,7 @@
         <v>87</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>37</v>
@@ -2367,7 +2346,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57">
+    <row r="8" spans="1:18" ht="57" hidden="1">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2421,7 +2400,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57">
+    <row r="9" spans="1:18" ht="57" hidden="1">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2475,7 +2454,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57">
+    <row r="10" spans="1:18" ht="57" hidden="1">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2529,7 +2508,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57">
+    <row r="11" spans="1:18" ht="57" hidden="1">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2583,7 +2562,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57">
+    <row r="12" spans="1:18" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
@@ -2637,7 +2616,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57">
+    <row r="13" spans="1:18" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2691,7 +2670,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57">
+    <row r="14" spans="1:18" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2745,7 +2724,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57">
+    <row r="15" spans="1:18" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2799,7 +2778,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57">
+    <row r="16" spans="1:18" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
@@ -2853,7 +2832,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="57">
+    <row r="17" spans="1:17" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -2907,7 +2886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="57">
+    <row r="18" spans="1:17" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2961,7 +2940,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="57">
+    <row r="19" spans="1:17" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
@@ -3015,7 +2994,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="57">
+    <row r="20" spans="1:17" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -3069,7 +3048,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="71.25">
+    <row r="21" spans="1:17" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>161</v>
       </c>
@@ -3121,7 +3100,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25">
+    <row r="22" spans="1:17" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -3173,7 +3152,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="71.25">
+    <row r="23" spans="1:17" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -3225,7 +3204,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="71.25">
+    <row r="24" spans="1:17" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -3277,7 +3256,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25">
+    <row r="25" spans="1:17" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -3329,7 +3308,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="71.25">
+    <row r="26" spans="1:17" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
@@ -3381,7 +3360,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="71.25">
+    <row r="27" spans="1:17" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -3433,7 +3412,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="71.25">
+    <row r="28" spans="1:17" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -3485,7 +3464,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="71.25">
+    <row r="29" spans="1:17" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>169</v>
       </c>
@@ -3537,7 +3516,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="71.25">
+    <row r="30" spans="1:17" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3589,7 +3568,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="71.25">
+    <row r="31" spans="1:17" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3641,7 +3620,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="71.25">
+    <row r="32" spans="1:17" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
@@ -3693,7 +3672,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="71.25">
+    <row r="33" spans="1:17" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>173</v>
       </c>
@@ -3745,7 +3724,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="71.25">
+    <row r="34" spans="1:17" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -3797,7 +3776,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="71.25">
+    <row r="35" spans="1:17" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>175</v>
       </c>
@@ -3849,7 +3828,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="85.5">
+    <row r="36" spans="1:17" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -3901,7 +3880,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="85.5">
+    <row r="37" spans="1:17" ht="85.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>177</v>
       </c>
@@ -3954,7 +3933,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="57">
+    <row r="38" spans="1:17" ht="57" hidden="1">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -4007,7 +3986,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="57">
+    <row r="39" spans="1:17" ht="57" hidden="1">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -4060,7 +4039,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57">
+    <row r="40" spans="1:17" ht="57" hidden="1">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -4113,7 +4092,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="57">
+    <row r="41" spans="1:17" ht="57" hidden="1">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -4166,7 +4145,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="57">
+    <row r="42" spans="1:17" ht="57" hidden="1">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -4219,7 +4198,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="85.5">
+    <row r="43" spans="1:17" ht="85.5" hidden="1">
       <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
@@ -4272,7 +4251,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="85.5">
+    <row r="44" spans="1:17" ht="85.5" hidden="1">
       <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
@@ -4325,7 +4304,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="85.5">
+    <row r="45" spans="1:17" ht="85.5" hidden="1">
       <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
@@ -4378,7 +4357,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="85.5">
+    <row r="46" spans="1:17" ht="85.5" hidden="1">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
@@ -4431,7 +4410,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="57">
+    <row r="47" spans="1:17" ht="57" hidden="1">
       <c r="A47" s="3" t="s">
         <v>216</v>
       </c>
@@ -4484,7 +4463,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="57">
+    <row r="48" spans="1:17" ht="57" hidden="1">
       <c r="A48" s="3" t="s">
         <v>221</v>
       </c>
@@ -4537,7 +4516,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="57">
+    <row r="49" spans="1:18" ht="57" hidden="1">
       <c r="A49" s="3" t="s">
         <v>224</v>
       </c>
@@ -4584,7 +4563,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="57">
+    <row r="50" spans="1:18" ht="57" hidden="1">
       <c r="A50" s="3" t="s">
         <v>228</v>
       </c>
@@ -4631,7 +4610,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="71.25">
+    <row r="51" spans="1:18" ht="71.25" hidden="1">
       <c r="A51" s="3" t="s">
         <v>370</v>
       </c>
@@ -4680,7 +4659,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="114">
+    <row r="52" spans="1:18" ht="114" hidden="1">
       <c r="A52" s="3" t="s">
         <v>236</v>
       </c>
@@ -4733,7 +4712,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="71.25">
+    <row r="53" spans="1:18" ht="71.25" hidden="1">
       <c r="A53" s="3" t="s">
         <v>333</v>
       </c>
@@ -4783,7 +4762,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="71.25">
+    <row r="54" spans="1:18" ht="71.25" hidden="1">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -4836,7 +4815,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="57">
+    <row r="55" spans="1:18" ht="57" hidden="1">
       <c r="A55" s="3" t="s">
         <v>351</v>
       </c>
@@ -4889,7 +4868,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="57">
+    <row r="56" spans="1:18" ht="57" hidden="1">
       <c r="A56" s="3" t="s">
         <v>361</v>
       </c>
@@ -4940,7 +4919,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="57">
+    <row r="57" spans="1:18" ht="57" hidden="1">
       <c r="A57" s="3" t="s">
         <v>371</v>
       </c>
@@ -4993,7 +4972,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="57">
+    <row r="58" spans="1:18" ht="57" hidden="1">
       <c r="A58" s="3" t="s">
         <v>375</v>
       </c>
@@ -5046,7 +5025,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="57">
+    <row r="59" spans="1:18" ht="57" hidden="1">
       <c r="A59" s="3" t="s">
         <v>394</v>
       </c>
@@ -5095,7 +5074,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="71.25">
+    <row r="60" spans="1:18" ht="71.25" hidden="1">
       <c r="A60" s="3" t="s">
         <v>73</v>
       </c>
@@ -5144,7 +5123,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="99.75">
+    <row r="61" spans="1:18" ht="99.75" hidden="1">
       <c r="A61" s="3" t="s">
         <v>407</v>
       </c>
@@ -5191,7 +5170,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="114">
+    <row r="62" spans="1:18" ht="114" hidden="1">
       <c r="A62" s="3" t="s">
         <v>412</v>
       </c>
@@ -5238,7 +5217,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="99.75">
+    <row r="63" spans="1:18" ht="57" hidden="1">
       <c r="A63" s="3" t="s">
         <v>423</v>
       </c>
@@ -5292,7 +5271,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="114">
+    <row r="64" spans="1:18" ht="57" hidden="1">
       <c r="A64" s="3" t="s">
         <v>431</v>
       </c>
@@ -5346,7 +5325,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="99.75">
+    <row r="65" spans="1:17" ht="57" hidden="1">
       <c r="A65" s="3" t="s">
         <v>432</v>
       </c>
@@ -5400,7 +5379,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="114">
+    <row r="66" spans="1:17" ht="57" hidden="1">
       <c r="A66" s="3" t="s">
         <v>433</v>
       </c>
@@ -5454,7 +5433,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="99.75">
+    <row r="67" spans="1:17" ht="57" hidden="1">
       <c r="A67" s="3" t="s">
         <v>434</v>
       </c>
@@ -5508,7 +5487,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="114">
+    <row r="68" spans="1:17" ht="85.5" hidden="1">
       <c r="A68" s="3" t="s">
         <v>453</v>
       </c>
@@ -5555,7 +5534,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="99.75">
+    <row r="69" spans="1:17" ht="85.5" hidden="1">
       <c r="A69" s="3" t="s">
         <v>463</v>
       </c>
@@ -5602,7 +5581,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="114">
+    <row r="70" spans="1:17" ht="85.5" hidden="1">
       <c r="A70" s="3" t="s">
         <v>468</v>
       </c>
@@ -5649,34 +5628,34 @@
         <v>472</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="99.75">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:17" ht="99.75" hidden="1">
+      <c r="A71" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <v>39.630000000000003</v>
       </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="8" t="s">
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="J71" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="6" t="s">
         <v>476</v>
       </c>
       <c r="L71" s="3" t="s">
@@ -5694,38 +5673,38 @@
       <c r="P71" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="Q71" s="7" t="s">
+      <c r="Q71" s="6" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="114">
-      <c r="A72" s="7" t="s">
+    <row r="72" spans="1:17" ht="114" hidden="1">
+      <c r="A72" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="6">
         <v>39.630000000000003</v>
       </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="s">
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="J72" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="K72" s="8" t="s">
+      <c r="K72" s="7" t="s">
         <v>477</v>
       </c>
       <c r="L72" s="3" t="s">
@@ -5743,7 +5722,7 @@
       <c r="P72" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="Q72" s="7" t="s">
+      <c r="Q72" s="6" t="s">
         <v>481</v>
       </c>
     </row>
@@ -5776,10 +5755,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F6431B-8687-4A20-A7DC-3A11C2AF4E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA34F74F-C100-444C-942E-2EEA318F017D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="490">
   <si>
     <t>TAG</t>
   </si>
@@ -1504,6 +1504,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/V12 - _KIT_FLANGE_CAR200M L_FF350.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/V12_KTRCAR225_SM_FF40.pdf</t>
   </si>
 </sst>
 </file>
@@ -1748,19 +1751,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="WCG20 - V/F12"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="10">
       <filters>
-        <filter val="Correia Transportadora - CT- 01"/>
-        <filter val="Correia Transportadora - CT- 02"/>
-        <filter val="Correia Transportadora - CT- 03"/>
-        <filter val="Correia Transportadora - CT- 04"/>
-        <filter val="Correia Transportadora - CT-08"/>
-        <filter val="Correia Transportadora - CT-09"/>
+        <filter val="Correia Transportadora - CT- 23"/>
+        <filter val="Correia Transportadora - CT-21"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1959,7 +1953,7 @@
     <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="18" style="2" customWidth="1"/>
     <col min="16" max="16" width="10.625" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" style="2" customWidth="1"/>
@@ -2238,7 +2232,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57">
+    <row r="6" spans="1:18" ht="57" hidden="1">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -2292,7 +2286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57">
+    <row r="7" spans="1:18" ht="57" hidden="1">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -2400,7 +2394,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57" hidden="1">
+    <row r="9" spans="1:18" ht="57">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2439,7 +2433,7 @@
         <v>88</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>37</v>
@@ -2454,7 +2448,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57" hidden="1">
+    <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2493,7 +2487,7 @@
         <v>88</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>37</v>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA34F74F-C100-444C-942E-2EEA318F017D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC8EEB6-DDDA-4FE8-ADCA-A618562AB47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="491">
   <si>
     <t>TAG</t>
   </si>
@@ -1507,6 +1507,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/V12_KTRCAR225_SM_FF40.pdf</t>
+  </si>
+  <si>
+    <t>RE-CT21</t>
   </si>
 </sst>
 </file>
@@ -2450,7 +2453,7 @@
     </row>
     <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>490</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>35</v>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC8EEB6-DDDA-4FE8-ADCA-A618562AB47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8A83B-B62F-4AA9-96E8-B3DAB87A0E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="492">
   <si>
     <t>TAG</t>
   </si>
@@ -1510,6 +1510,9 @@
   </si>
   <si>
     <t>RE-CT21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/V10_KTR400_C160180_FF300.pdf</t>
   </si>
 </sst>
 </file>
@@ -1754,10 +1757,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="10">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Correia Transportadora - CT- 23"/>
-        <filter val="Correia Transportadora - CT-21"/>
+        <filter val="RE-631501"/>
+        <filter val="RE-631502"/>
+        <filter val="RE-631503"/>
+        <filter val="RE-631504"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="WCG20 - V/F10"/>
+        <filter val="WCG20 F10 3"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2019,7 +2030,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57" hidden="1">
+    <row r="2" spans="1:18" ht="57">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -2058,7 +2069,7 @@
         <v>80</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>37</v>
@@ -2073,7 +2084,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57" hidden="1">
+    <row r="3" spans="1:18" ht="57">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -2112,7 +2123,7 @@
         <v>82</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>37</v>
@@ -2127,7 +2138,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57" hidden="1">
+    <row r="4" spans="1:18" ht="57">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -2166,7 +2177,7 @@
         <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>37</v>
@@ -2181,7 +2192,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57" hidden="1">
+    <row r="5" spans="1:18" ht="57">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2220,7 +2231,7 @@
         <v>84</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>37</v>
@@ -2397,7 +2408,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57">
+    <row r="9" spans="1:18" ht="57" hidden="1">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2451,7 +2462,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57">
+    <row r="10" spans="1:18" ht="57" hidden="1">
       <c r="A10" s="3" t="s">
         <v>490</v>
       </c>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8A83B-B62F-4AA9-96E8-B3DAB87A0E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35295CA-D741-45B6-AE6E-2B05D99BD831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1757,18 +1757,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="RE-631501"/>
-        <filter val="RE-631502"/>
-        <filter val="RE-631503"/>
-        <filter val="RE-631504"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="WCG20 - V/F10"/>
+        <filter val="WCG20 - V/F12"/>
         <filter val="WCG20 F10 3"/>
+        <filter val="WCG20 V/F12 3"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2246,7 +2240,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57" hidden="1">
+    <row r="6" spans="1:18" ht="57">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -2300,7 +2294,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57" hidden="1">
+    <row r="7" spans="1:18" ht="57">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -2354,7 +2348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57" hidden="1">
+    <row r="8" spans="1:18" ht="57">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2393,7 +2387,7 @@
         <v>85</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>37</v>
@@ -2408,7 +2402,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57" hidden="1">
+    <row r="9" spans="1:18" ht="57">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2462,7 +2456,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57" hidden="1">
+    <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
         <v>490</v>
       </c>
@@ -2516,7 +2510,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57" hidden="1">
+    <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2555,7 +2549,7 @@
         <v>88</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>37</v>
